--- a/customer_satisfaction_evaluation_forms/029_painter_and_decorator_feedback_form--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/029_painter_and_decorator_feedback_form--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -723,8 +723,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -752,12 +752,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_1,_'label':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 1, 'label': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -769,12 +769,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_2,_'label':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 2, 'label': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -786,12 +786,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_3,_'label':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 3, 'label': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_4,_'label':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 4, 'label': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'value':_5,_'label':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'value': 5, 'label': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'good',_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'good', 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'fair',_'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'fair', 'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'interior',_'label':_'interior'}</t>
+          <t>interior</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'interior', 'label': 'Interior'}</t>
+          <t>Interior</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'exterior',_'label':_'exterior'}</t>
+          <t>exterior</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'exterior', 'label': 'Exterior'}</t>
+          <t>Exterior</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'both',_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'both', 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
